--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O514"/>
+  <dimension ref="A1:O515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26640,6 +26640,57 @@
       <c r="O514" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>445.74</v>
+      </c>
+      <c r="C515" t="n">
+        <v>441.07</v>
+      </c>
+      <c r="D515" t="n">
+        <v>433.61</v>
+      </c>
+      <c r="E515" t="n">
+        <v>434.64</v>
+      </c>
+      <c r="F515" t="n">
+        <v>429.91</v>
+      </c>
+      <c r="G515" t="n">
+        <v>428.45</v>
+      </c>
+      <c r="H515" t="n">
+        <v>424.56</v>
+      </c>
+      <c r="I515" t="n">
+        <v>423.73</v>
+      </c>
+      <c r="J515" t="n">
+        <v>424.59</v>
+      </c>
+      <c r="K515" t="n">
+        <v>429.29</v>
+      </c>
+      <c r="L515" t="n">
+        <v>422.67</v>
+      </c>
+      <c r="M515" t="n">
+        <v>423.7</v>
+      </c>
+      <c r="N515" t="n">
+        <v>388.34</v>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26654,7 +26705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32057,6 +32108,16 @@
       </c>
       <c r="B540" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -32225,28 +32286,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.128293424430736</v>
+        <v>2.133004364590681</v>
       </c>
       <c r="J2" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6552263868585022</v>
+        <v>0.6567190420797238</v>
       </c>
       <c r="M2" t="n">
-        <v>8.945907655384424</v>
+        <v>8.95203871680962</v>
       </c>
       <c r="N2" t="n">
-        <v>132.6973150258186</v>
+        <v>132.7228980926016</v>
       </c>
       <c r="O2" t="n">
-        <v>11.51943206177365</v>
+        <v>11.52054243916499</v>
       </c>
       <c r="P2" t="n">
-        <v>377.7331604157879</v>
+        <v>377.6854414222954</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32303,28 +32364,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.169381472486597</v>
+        <v>2.174946717076445</v>
       </c>
       <c r="J3" t="n">
+        <v>514</v>
+      </c>
+      <c r="K3" t="n">
         <v>513</v>
       </c>
-      <c r="K3" t="n">
-        <v>512</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6776639342430273</v>
+        <v>0.6790321989543647</v>
       </c>
       <c r="M3" t="n">
-        <v>8.752857397109501</v>
+        <v>8.764420285006356</v>
       </c>
       <c r="N3" t="n">
-        <v>124.9330286540499</v>
+        <v>125.0880440621504</v>
       </c>
       <c r="O3" t="n">
-        <v>11.17734443658466</v>
+        <v>11.18427664456448</v>
       </c>
       <c r="P3" t="n">
-        <v>369.7503316164969</v>
+        <v>369.6940936583088</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32381,28 +32442,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.041844466348389</v>
+        <v>2.046475388517443</v>
       </c>
       <c r="J4" t="n">
+        <v>514</v>
+      </c>
+      <c r="K4" t="n">
         <v>513</v>
       </c>
-      <c r="K4" t="n">
-        <v>512</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6528184174554852</v>
+        <v>0.6543211219124434</v>
       </c>
       <c r="M4" t="n">
-        <v>9.084800211855898</v>
+        <v>9.091219681520489</v>
       </c>
       <c r="N4" t="n">
-        <v>123.7429547042659</v>
+        <v>123.7777020628798</v>
       </c>
       <c r="O4" t="n">
-        <v>11.123981063642</v>
+        <v>11.1255427761022</v>
       </c>
       <c r="P4" t="n">
-        <v>368.0443590483963</v>
+        <v>367.9975626132871</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32459,28 +32520,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.049278110358288</v>
+        <v>2.056330680270458</v>
       </c>
       <c r="J5" t="n">
+        <v>514</v>
+      </c>
+      <c r="K5" t="n">
         <v>513</v>
       </c>
-      <c r="K5" t="n">
-        <v>512</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6378672724621329</v>
+        <v>0.6393445967731362</v>
       </c>
       <c r="M5" t="n">
-        <v>9.269002786426825</v>
+        <v>9.289157620008815</v>
       </c>
       <c r="N5" t="n">
-        <v>133.0608044154774</v>
+        <v>133.4414688747614</v>
       </c>
       <c r="O5" t="n">
-        <v>11.53519849917969</v>
+        <v>11.55168684109647</v>
       </c>
       <c r="P5" t="n">
-        <v>362.6425730528852</v>
+        <v>362.5713053618725</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32537,28 +32598,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.248007774500612</v>
+        <v>2.254508929054685</v>
       </c>
       <c r="J6" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K6" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6404199158413171</v>
+        <v>0.6419555677641651</v>
       </c>
       <c r="M6" t="n">
-        <v>9.67293902886278</v>
+        <v>9.689642540644206</v>
       </c>
       <c r="N6" t="n">
-        <v>158.7391874087434</v>
+        <v>158.9757862170454</v>
       </c>
       <c r="O6" t="n">
-        <v>12.59917407645213</v>
+        <v>12.60856003741289</v>
       </c>
       <c r="P6" t="n">
-        <v>354.0714967122401</v>
+        <v>354.0059578489578</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32615,28 +32676,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.262265245018015</v>
+        <v>2.269455550569642</v>
       </c>
       <c r="J7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K7" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6229867680256733</v>
+        <v>0.624586310892364</v>
       </c>
       <c r="M7" t="n">
-        <v>10.04999843900144</v>
+        <v>10.0641547335267</v>
       </c>
       <c r="N7" t="n">
-        <v>174.1770954455751</v>
+        <v>174.5082386825722</v>
       </c>
       <c r="O7" t="n">
-        <v>13.19761703663109</v>
+        <v>13.21015664867651</v>
       </c>
       <c r="P7" t="n">
-        <v>350.4417495161618</v>
+        <v>350.3693943153581</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32693,28 +32754,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.295518590486119</v>
+        <v>2.3029988951933</v>
       </c>
       <c r="J8" t="n">
+        <v>514</v>
+      </c>
+      <c r="K8" t="n">
         <v>513</v>
       </c>
-      <c r="K8" t="n">
-        <v>512</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6298523550192476</v>
+        <v>0.63140594708804</v>
       </c>
       <c r="M8" t="n">
-        <v>10.10302539719275</v>
+        <v>10.11698412548583</v>
       </c>
       <c r="N8" t="n">
-        <v>173.5430367739772</v>
+        <v>173.9285697058304</v>
       </c>
       <c r="O8" t="n">
-        <v>13.17357342462466</v>
+        <v>13.18819812202677</v>
       </c>
       <c r="P8" t="n">
-        <v>344.9371876038674</v>
+        <v>344.8618224171661</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32771,28 +32832,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.149713976475528</v>
+        <v>2.158425511239755</v>
       </c>
       <c r="J9" t="n">
+        <v>514</v>
+      </c>
+      <c r="K9" t="n">
         <v>513</v>
       </c>
-      <c r="K9" t="n">
-        <v>512</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.5804582258827204</v>
+        <v>0.5822058779904788</v>
       </c>
       <c r="M9" t="n">
-        <v>10.68358053603538</v>
+        <v>10.70048061725196</v>
       </c>
       <c r="N9" t="n">
-        <v>187.1866756480294</v>
+        <v>187.8034998048252</v>
       </c>
       <c r="O9" t="n">
-        <v>13.68161816628535</v>
+        <v>13.70414170259579</v>
       </c>
       <c r="P9" t="n">
-        <v>344.752427009355</v>
+        <v>344.6646569960118</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32849,28 +32910,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.134933677845551</v>
+        <v>2.143981377749243</v>
       </c>
       <c r="J10" t="n">
+        <v>514</v>
+      </c>
+      <c r="K10" t="n">
         <v>513</v>
       </c>
-      <c r="K10" t="n">
-        <v>512</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.5632628932831176</v>
+        <v>0.5650942955859808</v>
       </c>
       <c r="M10" t="n">
-        <v>10.88458610094012</v>
+        <v>10.90378639495163</v>
       </c>
       <c r="N10" t="n">
-        <v>198.0555689134107</v>
+        <v>198.728433468918</v>
       </c>
       <c r="O10" t="n">
-        <v>14.07322169630717</v>
+        <v>14.09710727308684</v>
       </c>
       <c r="P10" t="n">
-        <v>345.1369133346326</v>
+        <v>345.0457564073212</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32927,28 +32988,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.118739051324372</v>
+        <v>2.129897490645374</v>
       </c>
       <c r="J11" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K11" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5631614004362151</v>
+        <v>0.5647871180410586</v>
       </c>
       <c r="M11" t="n">
-        <v>10.77456487649414</v>
+        <v>10.81249153929321</v>
       </c>
       <c r="N11" t="n">
-        <v>194.8053155631436</v>
+        <v>196.0331282131775</v>
       </c>
       <c r="O11" t="n">
-        <v>13.95726748196593</v>
+        <v>14.00118310048038</v>
       </c>
       <c r="P11" t="n">
-        <v>344.8183695018218</v>
+        <v>344.7058800319868</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33005,28 +33066,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.064918971385078</v>
+        <v>2.072523143982156</v>
       </c>
       <c r="J12" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K12" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5733235337364575</v>
+        <v>0.5751535048086813</v>
       </c>
       <c r="M12" t="n">
-        <v>10.549956373231</v>
+        <v>10.5644573650265</v>
       </c>
       <c r="N12" t="n">
-        <v>177.5262927398021</v>
+        <v>177.9271222852437</v>
       </c>
       <c r="O12" t="n">
-        <v>13.32389930687718</v>
+        <v>13.33893257668108</v>
       </c>
       <c r="P12" t="n">
-        <v>348.7929226251011</v>
+        <v>348.7162641140521</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33083,28 +33144,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>1.981952956736818</v>
+        <v>1.991821323744072</v>
       </c>
       <c r="J13" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K13" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4870936113595004</v>
+        <v>0.4893030654188473</v>
       </c>
       <c r="M13" t="n">
-        <v>11.35981001652165</v>
+        <v>11.3868664851513</v>
       </c>
       <c r="N13" t="n">
-        <v>231.4035906394721</v>
+        <v>232.2101381215875</v>
       </c>
       <c r="O13" t="n">
-        <v>15.21195551661495</v>
+        <v>15.23844277219912</v>
       </c>
       <c r="P13" t="n">
-        <v>346.1521900849343</v>
+        <v>346.0527059778071</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33165,28 +33226,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.661068130341711</v>
+        <v>1.660841344269924</v>
       </c>
       <c r="J14" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K14" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3615272083528039</v>
+        <v>0.3624623886907874</v>
       </c>
       <c r="M14" t="n">
-        <v>12.9695024786982</v>
+        <v>12.94561490238561</v>
       </c>
       <c r="N14" t="n">
-        <v>273.6165851936719</v>
+        <v>273.0817999201115</v>
       </c>
       <c r="O14" t="n">
-        <v>16.54135983508224</v>
+        <v>16.52518683465066</v>
       </c>
       <c r="P14" t="n">
-        <v>345.3027595734508</v>
+        <v>345.3050449393122</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -33228,7 +33289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O514"/>
+  <dimension ref="A1:O515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72753,6 +72814,83 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-36.90006301755777,174.44576594054493</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-36.899396208157285,174.44542611220055</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-36.89871835204975,174.4451144122726</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-36.89807408962427,174.44471711473355</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-36.89740702676591,174.4443778894873</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-36.896752899377155,174.44400569575976</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-36.896089150047324,174.44365800065307</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-36.89543750497283,174.4432794548335</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-36.89479137201789,174.44288315936453</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-36.89415848974034,174.44245144316469</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-36.89348203088608,174.44213598877272</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-36.892844316528596,174.44174860615595</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-36.892067875350314,174.4416986285087</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:O516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26677,7 +26677,7 @@
         <v>424.59</v>
       </c>
       <c r="K515" t="n">
-        <v>429.29</v>
+        <v>423.67</v>
       </c>
       <c r="L515" t="n">
         <v>422.67</v>
@@ -26691,6 +26691,57 @@
       <c r="O515" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>447.71</v>
+      </c>
+      <c r="C516" t="n">
+        <v>442.05</v>
+      </c>
+      <c r="D516" t="n">
+        <v>435.3</v>
+      </c>
+      <c r="E516" t="n">
+        <v>435.6</v>
+      </c>
+      <c r="F516" t="n">
+        <v>431.14</v>
+      </c>
+      <c r="G516" t="n">
+        <v>428.92</v>
+      </c>
+      <c r="H516" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="I516" t="n">
+        <v>421.58</v>
+      </c>
+      <c r="J516" t="n">
+        <v>422.61</v>
+      </c>
+      <c r="K516" t="n">
+        <v>421.92</v>
+      </c>
+      <c r="L516" t="n">
+        <v>422.82</v>
+      </c>
+      <c r="M516" t="n">
+        <v>424.42</v>
+      </c>
+      <c r="N516" t="n">
+        <v>393.31</v>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26705,7 +26756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32118,6 +32169,16 @@
       </c>
       <c r="B541" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -32286,28 +32347,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.133004364590681</v>
+        <v>2.138409420563642</v>
       </c>
       <c r="J2" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6567190420797238</v>
+        <v>0.6581915029872374</v>
       </c>
       <c r="M2" t="n">
-        <v>8.95203871680962</v>
+        <v>8.961704214186275</v>
       </c>
       <c r="N2" t="n">
-        <v>132.7228980926016</v>
+        <v>132.8415432965101</v>
       </c>
       <c r="O2" t="n">
-        <v>11.52054243916499</v>
+        <v>11.52569057785737</v>
       </c>
       <c r="P2" t="n">
-        <v>377.6854414222954</v>
+        <v>377.6306380605998</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32364,28 +32425,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.174946717076445</v>
+        <v>2.180814329331852</v>
       </c>
       <c r="J3" t="n">
+        <v>515</v>
+      </c>
+      <c r="K3" t="n">
         <v>514</v>
       </c>
-      <c r="K3" t="n">
-        <v>513</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6790321989543647</v>
+        <v>0.6803692921161989</v>
       </c>
       <c r="M3" t="n">
-        <v>8.764420285006356</v>
+        <v>8.777429139233055</v>
       </c>
       <c r="N3" t="n">
-        <v>125.0880440621504</v>
+        <v>125.2906843603142</v>
       </c>
       <c r="O3" t="n">
-        <v>11.18427664456448</v>
+        <v>11.19333213838999</v>
       </c>
       <c r="P3" t="n">
-        <v>369.6940936583088</v>
+        <v>369.6347423371321</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32442,28 +32503,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.046475388517443</v>
+        <v>2.051695346565031</v>
       </c>
       <c r="J4" t="n">
+        <v>515</v>
+      </c>
+      <c r="K4" t="n">
         <v>514</v>
       </c>
-      <c r="K4" t="n">
-        <v>513</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6543211219124434</v>
+        <v>0.6558036461143968</v>
       </c>
       <c r="M4" t="n">
-        <v>9.091219681520489</v>
+        <v>9.100624183714491</v>
       </c>
       <c r="N4" t="n">
-        <v>123.7777020628798</v>
+        <v>123.8898679204658</v>
       </c>
       <c r="O4" t="n">
-        <v>11.1255427761022</v>
+        <v>11.13058255081313</v>
       </c>
       <c r="P4" t="n">
-        <v>367.9975626132871</v>
+        <v>367.9447623611358</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32520,28 +32581,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.056330680270458</v>
+        <v>2.063661884596221</v>
       </c>
       <c r="J5" t="n">
+        <v>515</v>
+      </c>
+      <c r="K5" t="n">
         <v>514</v>
       </c>
-      <c r="K5" t="n">
-        <v>513</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6393445967731362</v>
+        <v>0.6407782486359446</v>
       </c>
       <c r="M5" t="n">
-        <v>9.289157620008815</v>
+        <v>9.311741072581846</v>
       </c>
       <c r="N5" t="n">
-        <v>133.4414688747614</v>
+        <v>133.8781046035586</v>
       </c>
       <c r="O5" t="n">
-        <v>11.55168684109647</v>
+        <v>11.57057062566746</v>
       </c>
       <c r="P5" t="n">
-        <v>362.5713053618725</v>
+        <v>362.4971497013397</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32598,28 +32659,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.254508929054685</v>
+        <v>2.261394936474033</v>
       </c>
       <c r="J6" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K6" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6419555677641651</v>
+        <v>0.6434578096419721</v>
       </c>
       <c r="M6" t="n">
-        <v>9.689642540644206</v>
+        <v>9.708525250960491</v>
       </c>
       <c r="N6" t="n">
-        <v>158.9757862170454</v>
+        <v>159.283113265741</v>
       </c>
       <c r="O6" t="n">
-        <v>12.60856003741289</v>
+        <v>12.62074139128684</v>
       </c>
       <c r="P6" t="n">
-        <v>354.0059578489578</v>
+        <v>353.9364714232059</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32676,28 +32737,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.269455550569642</v>
+        <v>2.276734255877049</v>
       </c>
       <c r="J7" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L7" t="n">
-        <v>0.624586310892364</v>
+        <v>0.626165556624469</v>
       </c>
       <c r="M7" t="n">
-        <v>10.0641547335267</v>
+        <v>10.0789344313929</v>
       </c>
       <c r="N7" t="n">
-        <v>174.5082386825722</v>
+        <v>174.8606328027767</v>
       </c>
       <c r="O7" t="n">
-        <v>13.21015664867651</v>
+        <v>13.22348792122474</v>
       </c>
       <c r="P7" t="n">
-        <v>350.3693943153581</v>
+        <v>350.2960773096587</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32754,28 +32815,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3029988951933</v>
+        <v>2.309972256190548</v>
       </c>
       <c r="J8" t="n">
+        <v>515</v>
+      </c>
+      <c r="K8" t="n">
         <v>514</v>
       </c>
-      <c r="K8" t="n">
-        <v>513</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.63140594708804</v>
+        <v>0.6329685282112708</v>
       </c>
       <c r="M8" t="n">
-        <v>10.11698412548583</v>
+        <v>10.12892349914906</v>
       </c>
       <c r="N8" t="n">
-        <v>173.9285697058304</v>
+        <v>174.2234401413888</v>
       </c>
       <c r="O8" t="n">
-        <v>13.18819812202677</v>
+        <v>13.1993727177237</v>
       </c>
       <c r="P8" t="n">
-        <v>344.8618224171661</v>
+        <v>344.7914959064171</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32832,28 +32893,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.158425511239755</v>
+        <v>2.166202329795452</v>
       </c>
       <c r="J9" t="n">
+        <v>515</v>
+      </c>
+      <c r="K9" t="n">
         <v>514</v>
       </c>
-      <c r="K9" t="n">
-        <v>513</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.5822058779904788</v>
+        <v>0.5839840302636277</v>
       </c>
       <c r="M9" t="n">
-        <v>10.70048061725196</v>
+        <v>10.71322825203043</v>
       </c>
       <c r="N9" t="n">
-        <v>187.8034998048252</v>
+        <v>188.2257071935275</v>
       </c>
       <c r="O9" t="n">
-        <v>13.70414170259579</v>
+        <v>13.71953742636855</v>
       </c>
       <c r="P9" t="n">
-        <v>344.6646569960118</v>
+        <v>344.5862275967643</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32910,28 +32971,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.143981377749243</v>
+        <v>2.152154092346535</v>
       </c>
       <c r="J10" t="n">
+        <v>515</v>
+      </c>
+      <c r="K10" t="n">
         <v>514</v>
       </c>
-      <c r="K10" t="n">
-        <v>513</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.5650942955859808</v>
+        <v>0.5669484303085733</v>
       </c>
       <c r="M10" t="n">
-        <v>10.90378639495163</v>
+        <v>10.91936661398652</v>
       </c>
       <c r="N10" t="n">
-        <v>198.728433468918</v>
+        <v>199.2116145537586</v>
       </c>
       <c r="O10" t="n">
-        <v>14.09710727308684</v>
+        <v>14.1142344657356</v>
       </c>
       <c r="P10" t="n">
-        <v>345.0457564073212</v>
+        <v>344.9633343871216</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32988,28 +33049,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.129897490645374</v>
+        <v>2.135916846388954</v>
       </c>
       <c r="J11" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K11" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5647871180410586</v>
+        <v>0.5668478962820793</v>
       </c>
       <c r="M11" t="n">
-        <v>10.81249153929321</v>
+        <v>10.82351291913199</v>
       </c>
       <c r="N11" t="n">
-        <v>196.0331282131775</v>
+        <v>195.960538375639</v>
       </c>
       <c r="O11" t="n">
-        <v>14.00118310048038</v>
+        <v>13.99859058532819</v>
       </c>
       <c r="P11" t="n">
-        <v>344.7058800319868</v>
+        <v>344.645117513955</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33066,28 +33127,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.072523143982156</v>
+        <v>2.080087043128189</v>
       </c>
       <c r="J12" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K12" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5751535048086813</v>
+        <v>0.576967187920404</v>
       </c>
       <c r="M12" t="n">
-        <v>10.5644573650265</v>
+        <v>10.58014489230997</v>
       </c>
       <c r="N12" t="n">
-        <v>177.9271222852437</v>
+        <v>178.3249082232278</v>
       </c>
       <c r="O12" t="n">
-        <v>13.33893257668108</v>
+        <v>13.35383496315676</v>
       </c>
       <c r="P12" t="n">
-        <v>348.7162641140521</v>
+        <v>348.63993710997</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33144,28 +33205,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>1.991821323744072</v>
+        <v>2.00184379706229</v>
       </c>
       <c r="J13" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K13" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4893030654188473</v>
+        <v>0.4914874676109288</v>
       </c>
       <c r="M13" t="n">
-        <v>11.3868664851513</v>
+        <v>11.41560114722576</v>
       </c>
       <c r="N13" t="n">
-        <v>232.2101381215875</v>
+        <v>233.0642376244398</v>
       </c>
       <c r="O13" t="n">
-        <v>15.23844277219912</v>
+        <v>15.26644155081464</v>
       </c>
       <c r="P13" t="n">
-        <v>346.0527059778071</v>
+        <v>345.951569599981</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33226,28 +33287,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.660841344269924</v>
+        <v>1.662515540137737</v>
       </c>
       <c r="J14" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K14" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3624623886907874</v>
+        <v>0.3638932695534355</v>
       </c>
       <c r="M14" t="n">
-        <v>12.94561490238561</v>
+        <v>12.9262153733879</v>
       </c>
       <c r="N14" t="n">
-        <v>273.0817999201115</v>
+        <v>272.5850807737301</v>
       </c>
       <c r="O14" t="n">
-        <v>16.52518683465066</v>
+        <v>16.51015084042935</v>
       </c>
       <c r="P14" t="n">
-        <v>345.3050449393122</v>
+        <v>345.2881571240884</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -33289,7 +33350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:O516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72867,7 +72928,7 @@
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>-36.89415848974034,174.44245144316469</t>
+          <t>-36.89413648485946,174.44250824409747</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -72888,6 +72949,83 @@
       <c r="O515" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-36.90007081387423,174.44574607848048</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-36.899400086510475,174.44541623165387</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-36.89872504020291,174.44509737350214</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-36.898077888790105,174.4447074359721</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-36.89741189442467,174.44436548866665</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-36.89675475936716,174.4440009572687</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-36.89608495519553,174.44366868738294</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-36.8954289965921,174.44330113059365</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-36.89478357226148,174.4429031428258</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-36.89412963280038,174.44252593121388</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-36.89348261735059,174.44213447223396</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-36.892847226868085,174.4417413851613</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-36.892088620055986,174.4416492018783</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O516"/>
+  <dimension ref="A1:O519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26740,6 +26740,159 @@
         <v>393.31</v>
       </c>
       <c r="O516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>449.58</v>
+      </c>
+      <c r="C517" t="n">
+        <v>444.05</v>
+      </c>
+      <c r="D517" t="n">
+        <v>436.99</v>
+      </c>
+      <c r="E517" t="n">
+        <v>436.73</v>
+      </c>
+      <c r="F517" t="n">
+        <v>431.72</v>
+      </c>
+      <c r="G517" t="n">
+        <v>429.36</v>
+      </c>
+      <c r="H517" t="n">
+        <v>423.32</v>
+      </c>
+      <c r="I517" t="n">
+        <v>419.62</v>
+      </c>
+      <c r="J517" t="n">
+        <v>420.18</v>
+      </c>
+      <c r="K517" t="n">
+        <v>419.73</v>
+      </c>
+      <c r="L517" t="n">
+        <v>422.41</v>
+      </c>
+      <c r="M517" t="n">
+        <v>424.64</v>
+      </c>
+      <c r="N517" t="n">
+        <v>397.06</v>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>449.58</v>
+      </c>
+      <c r="C518" t="n">
+        <v>444.05</v>
+      </c>
+      <c r="D518" t="n">
+        <v>436.99</v>
+      </c>
+      <c r="E518" t="n">
+        <v>436.73</v>
+      </c>
+      <c r="F518" t="n">
+        <v>431.72</v>
+      </c>
+      <c r="G518" t="n">
+        <v>429.36</v>
+      </c>
+      <c r="H518" t="n">
+        <v>423.32</v>
+      </c>
+      <c r="I518" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="J518" t="n">
+        <v>418.02</v>
+      </c>
+      <c r="K518" t="n">
+        <v>417.37</v>
+      </c>
+      <c r="L518" t="n">
+        <v>421.64</v>
+      </c>
+      <c r="M518" t="n">
+        <v>424.85</v>
+      </c>
+      <c r="N518" t="n">
+        <v>400.84</v>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>450.24</v>
+      </c>
+      <c r="C519" t="n">
+        <v>445.23</v>
+      </c>
+      <c r="D519" t="n">
+        <v>437.82</v>
+      </c>
+      <c r="E519" t="n">
+        <v>436.79</v>
+      </c>
+      <c r="F519" t="n">
+        <v>433.88</v>
+      </c>
+      <c r="G519" t="n">
+        <v>431.52</v>
+      </c>
+      <c r="H519" t="n">
+        <v>423.75</v>
+      </c>
+      <c r="I519" t="n">
+        <v>416.11</v>
+      </c>
+      <c r="J519" t="n">
+        <v>414.79</v>
+      </c>
+      <c r="K519" t="n">
+        <v>414.27</v>
+      </c>
+      <c r="L519" t="n">
+        <v>420.11</v>
+      </c>
+      <c r="M519" t="n">
+        <v>424.35</v>
+      </c>
+      <c r="N519" t="n">
+        <v>404.38</v>
+      </c>
+      <c r="O519" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -26756,7 +26909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32179,6 +32332,36 @@
       </c>
       <c r="B542" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -32347,28 +32530,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.138409420563642</v>
+        <v>2.156553358002989</v>
       </c>
       <c r="J2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K2" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6581915029872374</v>
+        <v>0.6624632868981071</v>
       </c>
       <c r="M2" t="n">
-        <v>8.961704214186275</v>
+        <v>9.000821631347533</v>
       </c>
       <c r="N2" t="n">
-        <v>132.8415432965101</v>
+        <v>133.4975396417901</v>
       </c>
       <c r="O2" t="n">
-        <v>11.52569057785737</v>
+        <v>11.55411353768822</v>
       </c>
       <c r="P2" t="n">
-        <v>377.6306380605998</v>
+        <v>377.4461326373558</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32425,28 +32608,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.180814329331852</v>
+        <v>2.20065288382566</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6803692921161989</v>
+        <v>0.6841299294894125</v>
       </c>
       <c r="M3" t="n">
-        <v>8.777429139233055</v>
+        <v>8.828302906036399</v>
       </c>
       <c r="N3" t="n">
-        <v>125.2906843603142</v>
+        <v>126.277204119726</v>
       </c>
       <c r="O3" t="n">
-        <v>11.19333213838999</v>
+        <v>11.23731302935564</v>
       </c>
       <c r="P3" t="n">
-        <v>369.6347423371321</v>
+        <v>369.4334836874229</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32503,28 +32686,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.051695346565031</v>
+        <v>2.069153186175835</v>
       </c>
       <c r="J4" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K4" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6558036461143968</v>
+        <v>0.6601094053089691</v>
       </c>
       <c r="M4" t="n">
-        <v>9.100624183714491</v>
+        <v>9.139454148627198</v>
       </c>
       <c r="N4" t="n">
-        <v>123.8898679204658</v>
+        <v>124.4974611165333</v>
       </c>
       <c r="O4" t="n">
-        <v>11.13058255081313</v>
+        <v>11.15784303154213</v>
       </c>
       <c r="P4" t="n">
-        <v>367.9447623611358</v>
+        <v>367.7676564845883</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32581,28 +32764,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.063661884596221</v>
+        <v>2.086397985958602</v>
       </c>
       <c r="J5" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K5" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6407782486359446</v>
+        <v>0.6449244461788659</v>
       </c>
       <c r="M5" t="n">
-        <v>9.311741072581846</v>
+        <v>9.383110224631594</v>
       </c>
       <c r="N5" t="n">
-        <v>133.8781046035586</v>
+        <v>135.3499886273862</v>
       </c>
       <c r="O5" t="n">
-        <v>11.57057062566746</v>
+        <v>11.63400140224275</v>
       </c>
       <c r="P5" t="n">
-        <v>362.4971497013397</v>
+        <v>362.2665008093877</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32659,28 +32842,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.261394936474033</v>
+        <v>2.282982599622859</v>
       </c>
       <c r="J6" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K6" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6434578096419721</v>
+        <v>0.6478286946440743</v>
       </c>
       <c r="M6" t="n">
-        <v>9.708525250960491</v>
+        <v>9.771122189593585</v>
       </c>
       <c r="N6" t="n">
-        <v>159.283113265741</v>
+        <v>160.3990424150062</v>
       </c>
       <c r="O6" t="n">
-        <v>12.62074139128684</v>
+        <v>12.66487435448951</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9364714232059</v>
+        <v>353.7179865620079</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32737,28 +32920,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.276734255877049</v>
+        <v>2.299308108969488</v>
       </c>
       <c r="J7" t="n">
+        <v>518</v>
+      </c>
+      <c r="K7" t="n">
         <v>515</v>
       </c>
-      <c r="K7" t="n">
-        <v>512</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.626165556624469</v>
+        <v>0.6307821390146555</v>
       </c>
       <c r="M7" t="n">
-        <v>10.0789344313929</v>
+        <v>10.12884295704887</v>
       </c>
       <c r="N7" t="n">
-        <v>174.8606328027767</v>
+        <v>176.0863733583666</v>
       </c>
       <c r="O7" t="n">
-        <v>13.22348792122474</v>
+        <v>13.26975408055351</v>
       </c>
       <c r="P7" t="n">
-        <v>350.2960773096587</v>
+        <v>350.0680162105015</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32815,28 +32998,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.309972256190548</v>
+        <v>2.330284424266078</v>
       </c>
       <c r="J8" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K8" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6329685282112708</v>
+        <v>0.637609500269809</v>
       </c>
       <c r="M8" t="n">
-        <v>10.12892349914906</v>
+        <v>10.16247120062473</v>
       </c>
       <c r="N8" t="n">
-        <v>174.2234401413888</v>
+        <v>175.0168479880892</v>
       </c>
       <c r="O8" t="n">
-        <v>13.1993727177237</v>
+        <v>13.22939333409092</v>
       </c>
       <c r="P8" t="n">
-        <v>344.7914959064171</v>
+        <v>344.5860451691452</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32893,28 +33076,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.166202329795452</v>
+        <v>2.184657836803447</v>
       </c>
       <c r="J9" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K9" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5839840302636277</v>
+        <v>0.5892835762254984</v>
       </c>
       <c r="M9" t="n">
-        <v>10.71322825203043</v>
+        <v>10.73033906382027</v>
       </c>
       <c r="N9" t="n">
-        <v>188.2257071935275</v>
+        <v>188.6359899381727</v>
       </c>
       <c r="O9" t="n">
-        <v>13.71953742636855</v>
+        <v>13.73448178629877</v>
       </c>
       <c r="P9" t="n">
-        <v>344.5862275967643</v>
+        <v>344.399571221627</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32971,28 +33154,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.152154092346535</v>
+        <v>2.170394989090474</v>
       </c>
       <c r="J10" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K10" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5669484303085733</v>
+        <v>0.5724133943987798</v>
       </c>
       <c r="M10" t="n">
-        <v>10.91936661398652</v>
+        <v>10.93736315006127</v>
       </c>
       <c r="N10" t="n">
-        <v>199.2116145537586</v>
+        <v>199.5408553661391</v>
       </c>
       <c r="O10" t="n">
-        <v>14.1142344657356</v>
+        <v>14.12589308207234</v>
       </c>
       <c r="P10" t="n">
-        <v>344.9633343871216</v>
+        <v>344.7788558589977</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33049,28 +33232,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.135916846388954</v>
+        <v>2.154398869603501</v>
       </c>
       <c r="J11" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K11" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5668478962820793</v>
+        <v>0.5723267196119791</v>
       </c>
       <c r="M11" t="n">
-        <v>10.82351291913199</v>
+        <v>10.8589469928219</v>
       </c>
       <c r="N11" t="n">
-        <v>195.960538375639</v>
+        <v>196.3464723333453</v>
       </c>
       <c r="O11" t="n">
-        <v>13.99859058532819</v>
+        <v>14.01236854829851</v>
       </c>
       <c r="P11" t="n">
-        <v>344.645117513955</v>
+        <v>344.4580919900907</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33127,28 +33310,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.080087043128189</v>
+        <v>2.100551264040478</v>
       </c>
       <c r="J12" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K12" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L12" t="n">
-        <v>0.576967187920404</v>
+        <v>0.5823730333899231</v>
       </c>
       <c r="M12" t="n">
-        <v>10.58014489230997</v>
+        <v>10.61925178040912</v>
       </c>
       <c r="N12" t="n">
-        <v>178.3249082232278</v>
+        <v>179.1251753968318</v>
       </c>
       <c r="O12" t="n">
-        <v>13.35383496315676</v>
+        <v>13.38376536692241</v>
       </c>
       <c r="P12" t="n">
-        <v>348.63993710997</v>
+        <v>348.4328388387848</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33205,28 +33388,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>2.00184379706229</v>
+        <v>2.031419425128826</v>
       </c>
       <c r="J13" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K13" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4914874676109288</v>
+        <v>0.4979587729832015</v>
       </c>
       <c r="M13" t="n">
-        <v>11.41560114722576</v>
+        <v>11.50286304400298</v>
       </c>
       <c r="N13" t="n">
-        <v>233.0642376244398</v>
+        <v>235.5309469095784</v>
       </c>
       <c r="O13" t="n">
-        <v>15.26644155081464</v>
+        <v>15.3470175248997</v>
       </c>
       <c r="P13" t="n">
-        <v>345.951569599981</v>
+        <v>345.6522520925778</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33287,28 +33470,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.662515540137737</v>
+        <v>1.675829234736112</v>
       </c>
       <c r="J14" t="n">
+        <v>518</v>
+      </c>
+      <c r="K14" t="n">
         <v>515</v>
       </c>
-      <c r="K14" t="n">
-        <v>512</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.3638932695534355</v>
+        <v>0.3698765998202801</v>
       </c>
       <c r="M14" t="n">
-        <v>12.9262153733879</v>
+        <v>12.89708423434743</v>
       </c>
       <c r="N14" t="n">
-        <v>272.5850807737301</v>
+        <v>271.8255867671992</v>
       </c>
       <c r="O14" t="n">
-        <v>16.51015084042935</v>
+        <v>16.48713397674681</v>
       </c>
       <c r="P14" t="n">
-        <v>345.2881571240884</v>
+        <v>345.1534365464979</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -33350,7 +33533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O516"/>
+  <dimension ref="A1:O519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73029,6 +73212,237 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-36.90007821443556,174.44572722463886</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-36.89940800151447,174.44539606726974</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-36.89873172835367,174.4450803347287</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-36.89808236072389,174.44469604326213</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-36.89741418974298,174.44435964112463</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-36.89675650063425,174.44399652123434</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-36.896084242862116,174.44367050211054</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-36.89542124011142,174.44332089081726</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-36.894773999828665,174.44292766797716</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-36.894121057934264,174.44254806537214</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-36.89348101434754,174.4421386174399</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-36.89284811613842,174.44173917874616</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-36.89210427248664,174.44161190812505</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-36.90007821443556,174.44572722463886</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-36.89940800151447,174.44539606726974</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-36.89873172835367,174.4450803347287</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-36.89808236072389,174.44469604326213</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-36.89741418974298,174.44435964112463</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-36.89675650063425,174.44399652123434</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-36.896084242862116,174.44367050211054</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-36.895414037662206,174.44333923959266</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-36.89476549099534,174.44294946810643</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-36.89411181743475,174.44257191770143</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-36.89347800382922,174.44214640233844</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>-36.89284896498732,174.44173707262257</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>-36.89212005012517,174.44157431600604</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-36.90008082639769,174.44572057034088</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-36.899412671365255,174.44538417028113</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-36.898735013065895,174.44507196657256</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-36.89808259817166,174.4446954383394</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-36.897422737822545,174.4443378640685</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-36.896765048670304,174.44397474433538</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-36.89608594454746,174.44366616692787</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-36.89540734967115,174.44335627773813</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-36.89475276713082,174.44298206736457</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-36.89409967948336,174.44260324914197</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-36.893472021888755,174.44216187103106</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>-36.892846943918435,174.44174208720247</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>-36.89213482599835,174.44153911067394</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O519"/>
+  <dimension ref="A1:O520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26895,6 +26895,57 @@
       <c r="O519" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>449.21</v>
+      </c>
+      <c r="C520" t="n">
+        <v>444.7</v>
+      </c>
+      <c r="D520" t="n">
+        <v>435.07</v>
+      </c>
+      <c r="E520" t="n">
+        <v>433.34</v>
+      </c>
+      <c r="F520" t="n">
+        <v>432.69</v>
+      </c>
+      <c r="G520" t="n">
+        <v>429.16</v>
+      </c>
+      <c r="H520" t="n">
+        <v>420.05</v>
+      </c>
+      <c r="I520" t="n">
+        <v>408.26</v>
+      </c>
+      <c r="J520" t="n">
+        <v>404.21</v>
+      </c>
+      <c r="K520" t="n">
+        <v>403.44</v>
+      </c>
+      <c r="L520" t="n">
+        <v>412.05</v>
+      </c>
+      <c r="M520" t="n">
+        <v>416.69</v>
+      </c>
+      <c r="N520" t="n">
+        <v>405.06</v>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32362,6 +32413,16 @@
       </c>
       <c r="B545" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -32530,28 +32591,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.156553358002989</v>
+        <v>2.162180193637738</v>
       </c>
       <c r="J2" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K2" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6624632868981071</v>
+        <v>0.6639113887622554</v>
       </c>
       <c r="M2" t="n">
-        <v>9.000821631347533</v>
+        <v>9.012345065149535</v>
       </c>
       <c r="N2" t="n">
-        <v>133.4975396417901</v>
+        <v>133.6497471680387</v>
       </c>
       <c r="O2" t="n">
-        <v>11.55411353768822</v>
+        <v>11.56069838582595</v>
       </c>
       <c r="P2" t="n">
-        <v>377.4461326373558</v>
+        <v>377.388532819328</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32608,28 +32669,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.20065288382566</v>
+        <v>2.207161642703876</v>
       </c>
       <c r="J3" t="n">
+        <v>519</v>
+      </c>
+      <c r="K3" t="n">
         <v>518</v>
       </c>
-      <c r="K3" t="n">
-        <v>517</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6841299294894125</v>
+        <v>0.6854015526830033</v>
       </c>
       <c r="M3" t="n">
-        <v>8.828302906036399</v>
+        <v>8.84470267825702</v>
       </c>
       <c r="N3" t="n">
-        <v>126.277204119726</v>
+        <v>126.5841992146349</v>
       </c>
       <c r="O3" t="n">
-        <v>11.23731302935564</v>
+        <v>11.25096436820573</v>
       </c>
       <c r="P3" t="n">
-        <v>369.4334836874229</v>
+        <v>369.3670144280267</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32686,28 +32747,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.069153186175835</v>
+        <v>2.073942801118338</v>
       </c>
       <c r="J4" t="n">
+        <v>519</v>
+      </c>
+      <c r="K4" t="n">
         <v>518</v>
       </c>
-      <c r="K4" t="n">
-        <v>517</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6601094053089691</v>
+        <v>0.6615823121017614</v>
       </c>
       <c r="M4" t="n">
-        <v>9.139454148627198</v>
+        <v>9.147161369015743</v>
       </c>
       <c r="N4" t="n">
-        <v>124.4974611165333</v>
+        <v>124.5553667441417</v>
       </c>
       <c r="O4" t="n">
-        <v>11.15784303154213</v>
+        <v>11.16043756956427</v>
       </c>
       <c r="P4" t="n">
-        <v>367.7676564845883</v>
+        <v>367.7187436021205</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32764,28 +32825,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.086397985958602</v>
+        <v>2.092458271779595</v>
       </c>
       <c r="J5" t="n">
+        <v>519</v>
+      </c>
+      <c r="K5" t="n">
         <v>518</v>
       </c>
-      <c r="K5" t="n">
-        <v>517</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6449244461788659</v>
+        <v>0.6464383541429342</v>
       </c>
       <c r="M5" t="n">
-        <v>9.383110224631594</v>
+        <v>9.397929983933876</v>
       </c>
       <c r="N5" t="n">
-        <v>135.3499886273862</v>
+        <v>135.566183662034</v>
       </c>
       <c r="O5" t="n">
-        <v>11.63400140224275</v>
+        <v>11.64328921147431</v>
       </c>
       <c r="P5" t="n">
-        <v>362.2665008093877</v>
+        <v>362.2046114818233</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32842,28 +32903,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.282982599622859</v>
+        <v>2.290059973303088</v>
       </c>
       <c r="J6" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K6" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6478286946440743</v>
+        <v>0.6493015611656636</v>
       </c>
       <c r="M6" t="n">
-        <v>9.771122189593585</v>
+        <v>9.79130797794544</v>
       </c>
       <c r="N6" t="n">
-        <v>160.3990424150062</v>
+        <v>160.7430952609707</v>
       </c>
       <c r="O6" t="n">
-        <v>12.66487435448951</v>
+        <v>12.67845003385551</v>
       </c>
       <c r="P6" t="n">
-        <v>353.7179865620079</v>
+        <v>353.6458821127189</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32920,28 +32981,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.299308108969488</v>
+        <v>2.306258759913686</v>
       </c>
       <c r="J7" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K7" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6307821390146555</v>
+        <v>0.6323568871402802</v>
       </c>
       <c r="M7" t="n">
-        <v>10.12884295704887</v>
+        <v>10.14278108275874</v>
       </c>
       <c r="N7" t="n">
-        <v>176.0863733583666</v>
+        <v>176.3795302417883</v>
       </c>
       <c r="O7" t="n">
-        <v>13.26975408055351</v>
+        <v>13.28079554250378</v>
       </c>
       <c r="P7" t="n">
-        <v>350.0680162105015</v>
+        <v>349.997323693065</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32998,28 +33059,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.330284424266078</v>
+        <v>2.33553691928726</v>
       </c>
       <c r="J8" t="n">
+        <v>519</v>
+      </c>
+      <c r="K8" t="n">
         <v>518</v>
       </c>
-      <c r="K8" t="n">
-        <v>517</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.637609500269809</v>
+        <v>0.6391748223737501</v>
       </c>
       <c r="M8" t="n">
-        <v>10.16247120062473</v>
+        <v>10.16733753675318</v>
       </c>
       <c r="N8" t="n">
-        <v>175.0168479880892</v>
+        <v>175.0395519967677</v>
       </c>
       <c r="O8" t="n">
-        <v>13.22939333409092</v>
+        <v>13.23025139582645</v>
       </c>
       <c r="P8" t="n">
-        <v>344.5860451691452</v>
+        <v>344.5325624787087</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33076,28 +33137,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.184657836803447</v>
+        <v>2.186941090114856</v>
       </c>
       <c r="J9" t="n">
+        <v>519</v>
+      </c>
+      <c r="K9" t="n">
         <v>518</v>
       </c>
-      <c r="K9" t="n">
-        <v>517</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.5892835762254984</v>
+        <v>0.5907512195881469</v>
       </c>
       <c r="M9" t="n">
-        <v>10.73033906382027</v>
+        <v>10.7192488070092</v>
       </c>
       <c r="N9" t="n">
-        <v>188.6359899381727</v>
+        <v>188.3399630289728</v>
       </c>
       <c r="O9" t="n">
-        <v>13.73448178629877</v>
+        <v>13.72370077744968</v>
       </c>
       <c r="P9" t="n">
-        <v>344.399571221627</v>
+        <v>344.3763223599813</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33154,28 +33215,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.170394989090474</v>
+        <v>2.171128219289375</v>
       </c>
       <c r="J10" t="n">
+        <v>519</v>
+      </c>
+      <c r="K10" t="n">
         <v>518</v>
       </c>
-      <c r="K10" t="n">
-        <v>517</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.5724133943987798</v>
+        <v>0.5736318792540955</v>
       </c>
       <c r="M10" t="n">
-        <v>10.93736315006127</v>
+        <v>10.91947088124162</v>
       </c>
       <c r="N10" t="n">
-        <v>199.5408553661391</v>
+        <v>199.1626679436594</v>
       </c>
       <c r="O10" t="n">
-        <v>14.12589308207234</v>
+        <v>14.11250041430148</v>
       </c>
       <c r="P10" t="n">
-        <v>344.7788558589977</v>
+        <v>344.7713898597748</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33232,28 +33293,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.154398869603501</v>
+        <v>2.155122561696047</v>
       </c>
       <c r="J11" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K11" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5723267196119791</v>
+        <v>0.5735451411476822</v>
       </c>
       <c r="M11" t="n">
-        <v>10.8589469928219</v>
+        <v>10.84185654737303</v>
       </c>
       <c r="N11" t="n">
-        <v>196.3464723333453</v>
+        <v>195.974984282309</v>
       </c>
       <c r="O11" t="n">
-        <v>14.01236854829851</v>
+        <v>13.99910655300219</v>
       </c>
       <c r="P11" t="n">
-        <v>344.4580919900907</v>
+        <v>344.4507189980536</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33310,28 +33371,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.100551264040478</v>
+        <v>2.103596391217397</v>
       </c>
       <c r="J12" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K12" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5823730333899231</v>
+        <v>0.5839686215256092</v>
       </c>
       <c r="M12" t="n">
-        <v>10.61925178040912</v>
+        <v>10.61372063108471</v>
       </c>
       <c r="N12" t="n">
-        <v>179.1251753968318</v>
+        <v>178.9009470251517</v>
       </c>
       <c r="O12" t="n">
-        <v>13.38376536692241</v>
+        <v>13.37538586453309</v>
       </c>
       <c r="P12" t="n">
-        <v>348.4328388387848</v>
+        <v>348.4018150115818</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33388,28 +33449,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>2.031419425128826</v>
+        <v>2.038011129634105</v>
       </c>
       <c r="J13" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K13" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4979587729832015</v>
+        <v>0.5000624819067448</v>
       </c>
       <c r="M13" t="n">
-        <v>11.50286304400298</v>
+        <v>11.51608222003203</v>
       </c>
       <c r="N13" t="n">
-        <v>235.5309469095784</v>
+        <v>235.6436764307681</v>
       </c>
       <c r="O13" t="n">
-        <v>15.3470175248997</v>
+        <v>15.35068977052068</v>
       </c>
       <c r="P13" t="n">
-        <v>345.6522520925778</v>
+        <v>345.5850956522508</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33470,28 +33531,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.675829234736112</v>
+        <v>1.681763989800252</v>
       </c>
       <c r="J14" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K14" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3698765998202801</v>
+        <v>0.3721402261712772</v>
       </c>
       <c r="M14" t="n">
-        <v>12.89708423434743</v>
+        <v>12.89265263086976</v>
       </c>
       <c r="N14" t="n">
-        <v>271.8255867671992</v>
+        <v>271.7608706036736</v>
       </c>
       <c r="O14" t="n">
-        <v>16.48713397674681</v>
+        <v>16.48517123367767</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1534365464979</v>
+        <v>345.0929910382503</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -33533,7 +33594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O519"/>
+  <dimension ref="A1:O520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73443,6 +73504,83 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-36.90007675015361,174.44573095507837</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-36.899410573890044,174.445389513844</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-36.898724129981005,174.44509969238825</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-36.898068944919316,174.44473022138806</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-36.89741802846439,174.44434986161394</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-36.89675570914925,174.44399853761362</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-36.8960713021337,174.44370346965582</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-36.895376284119344,174.44343541937977</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-36.894711089519575,174.44308884751976</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>-36.894057274899524,174.44271270696592</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-36.893440509150246,174.44224335965865</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>-36.89281598111741,174.4418189105331</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>-36.89213766430051,174.4415323480662</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O520"/>
+  <dimension ref="A1:O521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26946,6 +26946,57 @@
       <c r="O520" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>450.85</v>
+      </c>
+      <c r="C521" t="n">
+        <v>445.81</v>
+      </c>
+      <c r="D521" t="n">
+        <v>435.8</v>
+      </c>
+      <c r="E521" t="n">
+        <v>434.73</v>
+      </c>
+      <c r="F521" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="G521" t="n">
+        <v>431.31</v>
+      </c>
+      <c r="H521" t="n">
+        <v>422.74</v>
+      </c>
+      <c r="I521" t="n">
+        <v>409.41</v>
+      </c>
+      <c r="J521" t="n">
+        <v>404.02</v>
+      </c>
+      <c r="K521" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="L521" t="n">
+        <v>411.34</v>
+      </c>
+      <c r="M521" t="n">
+        <v>416.16</v>
+      </c>
+      <c r="N521" t="n">
+        <v>406.12</v>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26960,7 +27011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B546"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32423,6 +32474,16 @@
       </c>
       <c r="B546" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -32591,28 +32652,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.162180193637738</v>
+        <v>2.168363684562143</v>
       </c>
       <c r="J2" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K2" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6639113887622554</v>
+        <v>0.6653109327474087</v>
       </c>
       <c r="M2" t="n">
-        <v>9.012345065149535</v>
+        <v>9.027090720454616</v>
       </c>
       <c r="N2" t="n">
-        <v>133.6497471680387</v>
+        <v>133.8924176378006</v>
       </c>
       <c r="O2" t="n">
-        <v>11.56069838582595</v>
+        <v>11.57118911943801</v>
       </c>
       <c r="P2" t="n">
-        <v>377.388532819328</v>
+        <v>377.3252271666519</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32669,28 +32730,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.207161642703876</v>
+        <v>2.214012955607777</v>
       </c>
       <c r="J3" t="n">
+        <v>520</v>
+      </c>
+      <c r="K3" t="n">
         <v>519</v>
       </c>
-      <c r="K3" t="n">
-        <v>518</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6854015526830033</v>
+        <v>0.6866169752176251</v>
       </c>
       <c r="M3" t="n">
-        <v>8.84470267825702</v>
+        <v>8.862800132969882</v>
       </c>
       <c r="N3" t="n">
-        <v>126.5841992146349</v>
+        <v>126.9567688709579</v>
       </c>
       <c r="O3" t="n">
-        <v>11.25096436820573</v>
+        <v>11.26750943513951</v>
       </c>
       <c r="P3" t="n">
-        <v>369.3670144280267</v>
+        <v>369.2970385448183</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32747,28 +32808,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.073942801118338</v>
+        <v>2.07895040009232</v>
       </c>
       <c r="J4" t="n">
+        <v>520</v>
+      </c>
+      <c r="K4" t="n">
         <v>519</v>
       </c>
-      <c r="K4" t="n">
-        <v>518</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6615823121017614</v>
+        <v>0.6630336590060872</v>
       </c>
       <c r="M4" t="n">
-        <v>9.147161369015743</v>
+        <v>9.156118027714378</v>
       </c>
       <c r="N4" t="n">
-        <v>124.5553667441417</v>
+        <v>124.6446996230805</v>
       </c>
       <c r="O4" t="n">
-        <v>11.16043756956427</v>
+        <v>11.16443906441701</v>
       </c>
       <c r="P4" t="n">
-        <v>367.7187436021205</v>
+        <v>367.6675984908298</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32825,28 +32886,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.092458271779595</v>
+        <v>2.098973723356822</v>
       </c>
       <c r="J5" t="n">
+        <v>520</v>
+      </c>
+      <c r="K5" t="n">
         <v>519</v>
       </c>
-      <c r="K5" t="n">
-        <v>518</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6464383541429342</v>
+        <v>0.6479037288049896</v>
       </c>
       <c r="M5" t="n">
-        <v>9.397929983933876</v>
+        <v>9.415153131773669</v>
       </c>
       <c r="N5" t="n">
-        <v>135.566183662034</v>
+        <v>135.8624879328294</v>
       </c>
       <c r="O5" t="n">
-        <v>11.64328921147431</v>
+        <v>11.65600651736389</v>
       </c>
       <c r="P5" t="n">
-        <v>362.2046114818233</v>
+        <v>362.1380659182192</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32903,28 +32964,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.290059973303088</v>
+        <v>2.297776621801346</v>
       </c>
       <c r="J6" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K6" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6493015611656636</v>
+        <v>0.6507031182590312</v>
       </c>
       <c r="M6" t="n">
-        <v>9.79130797794544</v>
+        <v>9.815093250933389</v>
       </c>
       <c r="N6" t="n">
-        <v>160.7430952609707</v>
+        <v>161.2182735266368</v>
       </c>
       <c r="O6" t="n">
-        <v>12.67845003385551</v>
+        <v>12.69717580907805</v>
       </c>
       <c r="P6" t="n">
-        <v>353.6458821127189</v>
+        <v>353.5672553068156</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32981,28 +33042,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.306258759913686</v>
+        <v>2.313940911052373</v>
       </c>
       <c r="J7" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K7" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6323568871402802</v>
+        <v>0.6338701448072452</v>
       </c>
       <c r="M7" t="n">
-        <v>10.14278108275874</v>
+        <v>10.16104683171651</v>
       </c>
       <c r="N7" t="n">
-        <v>176.3795302417883</v>
+        <v>176.821198213783</v>
       </c>
       <c r="O7" t="n">
-        <v>13.28079554250378</v>
+        <v>13.29741321512508</v>
       </c>
       <c r="P7" t="n">
-        <v>349.997323693065</v>
+        <v>349.9191819149743</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33059,28 +33120,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.33553691928726</v>
+        <v>2.341746820346148</v>
       </c>
       <c r="J8" t="n">
+        <v>520</v>
+      </c>
+      <c r="K8" t="n">
         <v>519</v>
       </c>
-      <c r="K8" t="n">
-        <v>518</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6391748223737501</v>
+        <v>0.6407202929603252</v>
       </c>
       <c r="M8" t="n">
-        <v>10.16733753675318</v>
+        <v>10.17664956255506</v>
       </c>
       <c r="N8" t="n">
-        <v>175.0395519967677</v>
+        <v>175.2114045928028</v>
       </c>
       <c r="O8" t="n">
-        <v>13.23025139582645</v>
+        <v>13.23674448619459</v>
       </c>
       <c r="P8" t="n">
-        <v>344.5325624787087</v>
+        <v>344.469323562337</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33137,28 +33198,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.186941090114856</v>
+        <v>2.189633419763119</v>
       </c>
       <c r="J9" t="n">
+        <v>520</v>
+      </c>
+      <c r="K9" t="n">
         <v>519</v>
       </c>
-      <c r="K9" t="n">
-        <v>518</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.5907512195881469</v>
+        <v>0.592263393401351</v>
       </c>
       <c r="M9" t="n">
-        <v>10.7192488070092</v>
+        <v>10.70991890939941</v>
       </c>
       <c r="N9" t="n">
-        <v>188.3399630289728</v>
+        <v>188.0727710890137</v>
       </c>
       <c r="O9" t="n">
-        <v>13.72370077744968</v>
+        <v>13.71396263262423</v>
       </c>
       <c r="P9" t="n">
-        <v>344.3763223599813</v>
+        <v>344.3489048523821</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33215,28 +33276,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.171128219289375</v>
+        <v>2.171778142590968</v>
       </c>
       <c r="J10" t="n">
+        <v>520</v>
+      </c>
+      <c r="K10" t="n">
         <v>519</v>
       </c>
-      <c r="K10" t="n">
-        <v>518</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.5736318792540955</v>
+        <v>0.5748242973377726</v>
       </c>
       <c r="M10" t="n">
-        <v>10.91947088124162</v>
+        <v>10.90128133377589</v>
       </c>
       <c r="N10" t="n">
-        <v>199.1626679436594</v>
+        <v>198.7845014692788</v>
       </c>
       <c r="O10" t="n">
-        <v>14.11250041430148</v>
+        <v>14.09909576778876</v>
       </c>
       <c r="P10" t="n">
-        <v>344.7713898597748</v>
+        <v>344.7647713251271</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33293,28 +33354,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.155122561696047</v>
+        <v>2.155475852283153</v>
       </c>
       <c r="J11" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K11" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5735451411476822</v>
+        <v>0.5746769470782742</v>
       </c>
       <c r="M11" t="n">
-        <v>10.84185654737303</v>
+        <v>10.82287364906421</v>
       </c>
       <c r="N11" t="n">
-        <v>195.974984282309</v>
+        <v>195.5997532628653</v>
       </c>
       <c r="O11" t="n">
-        <v>13.99910655300219</v>
+        <v>13.9856981685887</v>
       </c>
       <c r="P11" t="n">
-        <v>344.4507189980536</v>
+        <v>344.4471192344482</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33371,28 +33432,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.103596391217397</v>
+        <v>2.106332942142779</v>
       </c>
       <c r="J12" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K12" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5839686215256092</v>
+        <v>0.5855123024015987</v>
       </c>
       <c r="M12" t="n">
-        <v>10.61372063108471</v>
+        <v>10.60670564000877</v>
       </c>
       <c r="N12" t="n">
-        <v>178.9009470251517</v>
+        <v>178.6555418738745</v>
       </c>
       <c r="O12" t="n">
-        <v>13.37538586453309</v>
+        <v>13.36620895668905</v>
       </c>
       <c r="P12" t="n">
-        <v>348.4018150115818</v>
+        <v>348.3739316295017</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33449,28 +33510,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>2.038011129634105</v>
+        <v>2.044318437129089</v>
       </c>
       <c r="J13" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K13" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5000624819067448</v>
+        <v>0.5021285182420037</v>
       </c>
       <c r="M13" t="n">
-        <v>11.51608222003203</v>
+        <v>11.52772496343118</v>
       </c>
       <c r="N13" t="n">
-        <v>235.6436764307681</v>
+        <v>235.7144929288547</v>
       </c>
       <c r="O13" t="n">
-        <v>15.35068977052068</v>
+        <v>15.35299621991925</v>
       </c>
       <c r="P13" t="n">
-        <v>345.5850956522508</v>
+        <v>345.5208289641554</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33531,28 +33592,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.681763989800252</v>
+        <v>1.688029250884275</v>
       </c>
       <c r="J14" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K14" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3721402261712772</v>
+        <v>0.3744373924988361</v>
       </c>
       <c r="M14" t="n">
-        <v>12.89265263086976</v>
+        <v>12.88947443728105</v>
       </c>
       <c r="N14" t="n">
-        <v>271.7608706036736</v>
+        <v>271.7554168455354</v>
       </c>
       <c r="O14" t="n">
-        <v>16.48517123367767</v>
+        <v>16.48500581878985</v>
       </c>
       <c r="P14" t="n">
-        <v>345.0929910382503</v>
+        <v>345.0291716204651</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -33594,7 +33655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O520"/>
+  <dimension ref="A1:O521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73581,6 +73642,83 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-36.90008324048358,174.445714420156</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-36.89941496671522,174.4453783226082</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-36.898727018945976,174.44509233244523</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-36.89807444579609,174.44471620734967</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-36.897425587181516,174.44433060504872</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-36.896764217611405,174.44397686153408</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-36.89608194756537,174.4436763495659</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-36.895380835126964,174.4434238253854</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-36.89471034105499,174.44309076512073</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>-36.894053594349266,174.44272220745447</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-36.89343773321161,174.442250537934</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>-36.89281383878082,174.44182422598314</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>-36.89214208871195,174.4415218063531</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O521"/>
+  <dimension ref="A1:O522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26995,6 +26995,57 @@
         <v>406.12</v>
       </c>
       <c r="O521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>459.54</v>
+      </c>
+      <c r="C522" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="D522" t="n">
+        <v>442.16</v>
+      </c>
+      <c r="E522" t="n">
+        <v>438.67</v>
+      </c>
+      <c r="F522" t="n">
+        <v>439.36</v>
+      </c>
+      <c r="G522" t="n">
+        <v>434.36</v>
+      </c>
+      <c r="H522" t="n">
+        <v>423.08</v>
+      </c>
+      <c r="I522" t="n">
+        <v>404.17</v>
+      </c>
+      <c r="J522" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="K522" t="n">
+        <v>395</v>
+      </c>
+      <c r="L522" t="n">
+        <v>409.71</v>
+      </c>
+      <c r="M522" t="n">
+        <v>420.53</v>
+      </c>
+      <c r="N522" t="n">
+        <v>421.77</v>
+      </c>
+      <c r="O522" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27011,7 +27062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B547"/>
+  <dimension ref="A1:B548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32484,6 +32535,16 @@
       </c>
       <c r="B547" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -32652,28 +32713,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.168363684562143</v>
+        <v>2.177775018828601</v>
       </c>
       <c r="J2" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K2" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6653109327474087</v>
+        <v>0.6662793095192718</v>
       </c>
       <c r="M2" t="n">
-        <v>9.027090720454616</v>
+        <v>9.059047607170603</v>
       </c>
       <c r="N2" t="n">
-        <v>133.8924176378006</v>
+        <v>134.7935566022414</v>
       </c>
       <c r="O2" t="n">
-        <v>11.57118911943801</v>
+        <v>11.61006273033188</v>
       </c>
       <c r="P2" t="n">
-        <v>377.3252271666519</v>
+        <v>377.2286105116413</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32730,28 +32791,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.214012955607777</v>
+        <v>2.223086796736546</v>
       </c>
       <c r="J3" t="n">
+        <v>521</v>
+      </c>
+      <c r="K3" t="n">
         <v>520</v>
       </c>
-      <c r="K3" t="n">
-        <v>519</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6866169752176251</v>
+        <v>0.6874796701316161</v>
       </c>
       <c r="M3" t="n">
-        <v>8.862800132969882</v>
+        <v>8.89286293462532</v>
       </c>
       <c r="N3" t="n">
-        <v>126.9567688709579</v>
+        <v>127.7932700588241</v>
       </c>
       <c r="O3" t="n">
-        <v>11.26750943513951</v>
+        <v>11.30456854810585</v>
       </c>
       <c r="P3" t="n">
-        <v>369.2970385448183</v>
+        <v>369.2041079076121</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32808,28 +32869,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.07895040009232</v>
+        <v>2.086298640533878</v>
       </c>
       <c r="J4" t="n">
+        <v>521</v>
+      </c>
+      <c r="K4" t="n">
         <v>520</v>
       </c>
-      <c r="K4" t="n">
-        <v>519</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6630336590060872</v>
+        <v>0.664306095462868</v>
       </c>
       <c r="M4" t="n">
-        <v>9.156118027714378</v>
+        <v>9.177373655028408</v>
       </c>
       <c r="N4" t="n">
-        <v>124.6446996230805</v>
+        <v>125.1137089265214</v>
       </c>
       <c r="O4" t="n">
-        <v>11.16443906441701</v>
+        <v>11.18542394934235</v>
       </c>
       <c r="P4" t="n">
-        <v>367.6675984908298</v>
+        <v>367.5923407629406</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32886,28 +32947,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.098973723356822</v>
+        <v>2.106896130845866</v>
       </c>
       <c r="J5" t="n">
+        <v>521</v>
+      </c>
+      <c r="K5" t="n">
         <v>520</v>
       </c>
-      <c r="K5" t="n">
-        <v>519</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6479037288049896</v>
+        <v>0.6492262608602621</v>
       </c>
       <c r="M5" t="n">
-        <v>9.415153131773669</v>
+        <v>9.439693601991834</v>
       </c>
       <c r="N5" t="n">
-        <v>135.8624879328294</v>
+        <v>136.4250040674177</v>
       </c>
       <c r="O5" t="n">
-        <v>11.65600651736389</v>
+        <v>11.68011147495681</v>
       </c>
       <c r="P5" t="n">
-        <v>362.1380659182192</v>
+        <v>362.0569278019885</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32964,28 +33025,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.297776621801346</v>
+        <v>2.30719783586745</v>
       </c>
       <c r="J6" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K6" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6507031182590312</v>
+        <v>0.6519002095172906</v>
       </c>
       <c r="M6" t="n">
-        <v>9.815093250933389</v>
+        <v>9.84791664312505</v>
       </c>
       <c r="N6" t="n">
-        <v>161.2182735266368</v>
+        <v>162.0772084257839</v>
       </c>
       <c r="O6" t="n">
-        <v>12.69717580907805</v>
+        <v>12.73095473347478</v>
       </c>
       <c r="P6" t="n">
-        <v>353.5672553068156</v>
+        <v>353.470995926392</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33042,28 +33103,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.313940911052373</v>
+        <v>2.322676754314356</v>
       </c>
       <c r="J7" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K7" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6338701448072452</v>
+        <v>0.635292535235882</v>
       </c>
       <c r="M7" t="n">
-        <v>10.16104683171651</v>
+        <v>10.18449895481355</v>
       </c>
       <c r="N7" t="n">
-        <v>176.821198213783</v>
+        <v>177.4915286116896</v>
       </c>
       <c r="O7" t="n">
-        <v>13.29741321512508</v>
+        <v>13.32259466514273</v>
       </c>
       <c r="P7" t="n">
-        <v>349.9191819149743</v>
+        <v>349.8300751005897</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33120,28 +33181,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.341746820346148</v>
+        <v>2.347987514808462</v>
       </c>
       <c r="J8" t="n">
+        <v>521</v>
+      </c>
+      <c r="K8" t="n">
         <v>520</v>
       </c>
-      <c r="K8" t="n">
-        <v>519</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6407202929603252</v>
+        <v>0.64226303007901</v>
       </c>
       <c r="M8" t="n">
-        <v>10.17664956255506</v>
+        <v>10.18590949265919</v>
       </c>
       <c r="N8" t="n">
-        <v>175.2114045928028</v>
+        <v>175.388330237238</v>
       </c>
       <c r="O8" t="n">
-        <v>13.23674448619459</v>
+        <v>13.24342592523695</v>
       </c>
       <c r="P8" t="n">
-        <v>344.469323562337</v>
+        <v>344.4055955022934</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33198,28 +33259,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.189633419763119</v>
+        <v>2.190259643533627</v>
       </c>
       <c r="J9" t="n">
+        <v>521</v>
+      </c>
+      <c r="K9" t="n">
         <v>520</v>
       </c>
-      <c r="K9" t="n">
-        <v>519</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.592263393401351</v>
+        <v>0.5934374177520625</v>
       </c>
       <c r="M9" t="n">
-        <v>10.70991890939941</v>
+        <v>10.691933397213</v>
       </c>
       <c r="N9" t="n">
-        <v>188.0727710890137</v>
+        <v>187.7162669290742</v>
       </c>
       <c r="O9" t="n">
-        <v>13.71396263262423</v>
+        <v>13.70095861350855</v>
       </c>
       <c r="P9" t="n">
-        <v>344.3489048523821</v>
+        <v>344.3425100470783</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33276,28 +33337,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.171778142590968</v>
+        <v>2.1695827359836</v>
       </c>
       <c r="J10" t="n">
+        <v>521</v>
+      </c>
+      <c r="K10" t="n">
         <v>520</v>
       </c>
-      <c r="K10" t="n">
-        <v>519</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.5748242973377726</v>
+        <v>0.5753072170571576</v>
       </c>
       <c r="M10" t="n">
-        <v>10.90128133377589</v>
+        <v>10.89282156003614</v>
       </c>
       <c r="N10" t="n">
-        <v>198.7845014692788</v>
+        <v>198.4658178405093</v>
       </c>
       <c r="O10" t="n">
-        <v>14.09909576778876</v>
+        <v>14.087789671929</v>
       </c>
       <c r="P10" t="n">
-        <v>344.7647713251271</v>
+        <v>344.7871901448496</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33354,28 +33415,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.155475852283153</v>
+        <v>2.152921020087732</v>
       </c>
       <c r="J11" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K11" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5746769470782742</v>
+        <v>0.5750460836033673</v>
       </c>
       <c r="M11" t="n">
-        <v>10.82287364906421</v>
+        <v>10.81430643556329</v>
       </c>
       <c r="N11" t="n">
-        <v>195.5997532628653</v>
+        <v>195.310241675014</v>
       </c>
       <c r="O11" t="n">
-        <v>13.9856981685887</v>
+        <v>13.97534406284919</v>
       </c>
       <c r="P11" t="n">
-        <v>344.4471192344482</v>
+        <v>344.4732227241356</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33432,28 +33493,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.106332942142779</v>
+        <v>2.108378930051924</v>
       </c>
       <c r="J12" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K12" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5855123024015987</v>
+        <v>0.5869568049892531</v>
       </c>
       <c r="M12" t="n">
-        <v>10.60670564000877</v>
+        <v>10.59628124558223</v>
       </c>
       <c r="N12" t="n">
-        <v>178.6555418738745</v>
+        <v>178.367735885699</v>
       </c>
       <c r="O12" t="n">
-        <v>13.36620895668905</v>
+        <v>13.35543843854252</v>
       </c>
       <c r="P12" t="n">
-        <v>348.3739316295017</v>
+        <v>348.3530271550777</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33510,28 +33571,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>2.044318437129089</v>
+        <v>2.052195031102307</v>
       </c>
       <c r="J13" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K13" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5021285182420037</v>
+        <v>0.50426545374945</v>
       </c>
       <c r="M13" t="n">
-        <v>11.52772496343118</v>
+        <v>11.54776085474913</v>
       </c>
       <c r="N13" t="n">
-        <v>235.7144929288547</v>
+        <v>236.0787336485592</v>
       </c>
       <c r="O13" t="n">
-        <v>15.35299621991925</v>
+        <v>15.36485384403507</v>
       </c>
       <c r="P13" t="n">
-        <v>345.5208289641554</v>
+        <v>345.4403514322374</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33592,28 +33653,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.688029250884275</v>
+        <v>1.700168307559208</v>
       </c>
       <c r="J14" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K14" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3744373924988361</v>
+        <v>0.3771285686566356</v>
       </c>
       <c r="M14" t="n">
-        <v>12.88947443728105</v>
+        <v>12.90636778905217</v>
       </c>
       <c r="N14" t="n">
-        <v>271.7554168455354</v>
+        <v>273.1823705948286</v>
       </c>
       <c r="O14" t="n">
-        <v>16.48500581878985</v>
+        <v>16.52822950575253</v>
       </c>
       <c r="P14" t="n">
-        <v>345.0291716204651</v>
+        <v>344.9051768848904</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -33655,7 +33716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O521"/>
+  <dimension ref="A1:O522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73719,6 +73780,83 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-36.9001176312799,174.4456268051843</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-36.89943906787285,174.44531692202094</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-36.89875218853971,174.445028210178</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-36.89809003820065,174.4446764840931</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-36.89744442459944,174.4442826148483</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-36.8967762877488,174.4439461117384</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-36.89608329308418,174.44367292174726</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-36.89536009835283,174.44347665366135</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-36.8946815054494,174.4431646431912</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>-36.894024228230286,174.44279800919165</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>-36.89343136028045,174.4422670176345</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>-36.892831502945384,174.44178039858414</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>-36.892207411284076,174.44136616676545</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0183/nzd0183.xlsx
+++ b/data/nzd0183/nzd0183.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O522"/>
+  <dimension ref="A1:O528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27048,6 +27048,312 @@
       <c r="O522" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>459.54</v>
+      </c>
+      <c r="C523" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="D523" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="E523" t="n">
+        <v>438.67</v>
+      </c>
+      <c r="F523" t="n">
+        <v>439.36</v>
+      </c>
+      <c r="G523" t="n">
+        <v>434.36</v>
+      </c>
+      <c r="H523" t="n">
+        <v>423.08</v>
+      </c>
+      <c r="I523" t="n">
+        <v>404.17</v>
+      </c>
+      <c r="J523" t="n">
+        <v>402.4</v>
+      </c>
+      <c r="K523" t="n">
+        <v>399.92</v>
+      </c>
+      <c r="L523" t="n">
+        <v>413.29</v>
+      </c>
+      <c r="M523" t="n">
+        <v>420.53</v>
+      </c>
+      <c r="N523" t="n">
+        <v>421.77</v>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>458.37</v>
+      </c>
+      <c r="C524" t="n">
+        <v>452.76</v>
+      </c>
+      <c r="D524" t="n">
+        <v>444.3</v>
+      </c>
+      <c r="E524" t="n">
+        <v>439.94</v>
+      </c>
+      <c r="F524" t="n">
+        <v>438.67</v>
+      </c>
+      <c r="G524" t="n">
+        <v>433.27</v>
+      </c>
+      <c r="H524" t="n">
+        <v>422.47</v>
+      </c>
+      <c r="I524" t="n">
+        <v>405.48</v>
+      </c>
+      <c r="J524" t="n">
+        <v>403.06</v>
+      </c>
+      <c r="K524" t="n">
+        <v>400.79</v>
+      </c>
+      <c r="L524" t="n">
+        <v>413.72</v>
+      </c>
+      <c r="M524" t="n">
+        <v>420.45</v>
+      </c>
+      <c r="N524" t="n">
+        <v>421.08</v>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>458.62</v>
+      </c>
+      <c r="C525" t="n">
+        <v>453.13</v>
+      </c>
+      <c r="D525" t="n">
+        <v>445.79</v>
+      </c>
+      <c r="E525" t="n">
+        <v>441.88</v>
+      </c>
+      <c r="F525" t="n">
+        <v>438.77</v>
+      </c>
+      <c r="G525" t="n">
+        <v>434.18</v>
+      </c>
+      <c r="H525" t="n">
+        <v>423.21</v>
+      </c>
+      <c r="I525" t="n">
+        <v>407.57</v>
+      </c>
+      <c r="J525" t="n">
+        <v>404.86</v>
+      </c>
+      <c r="K525" t="n">
+        <v>402.54</v>
+      </c>
+      <c r="L525" t="n">
+        <v>415.08</v>
+      </c>
+      <c r="M525" t="n">
+        <v>421.46</v>
+      </c>
+      <c r="N525" t="n">
+        <v>421.84</v>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>458.92</v>
+      </c>
+      <c r="C526" t="n">
+        <v>454.16</v>
+      </c>
+      <c r="D526" t="n">
+        <v>446.91</v>
+      </c>
+      <c r="E526" t="n">
+        <v>443.79</v>
+      </c>
+      <c r="F526" t="n">
+        <v>438.29</v>
+      </c>
+      <c r="G526" t="n">
+        <v>434.11</v>
+      </c>
+      <c r="H526" t="n">
+        <v>423.99</v>
+      </c>
+      <c r="I526" t="n">
+        <v>409.01</v>
+      </c>
+      <c r="J526" t="n">
+        <v>406.17</v>
+      </c>
+      <c r="K526" t="n">
+        <v>404.38</v>
+      </c>
+      <c r="L526" t="n">
+        <v>416.9</v>
+      </c>
+      <c r="M526" t="n">
+        <v>422.48</v>
+      </c>
+      <c r="N526" t="n">
+        <v>422.29</v>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>460.91</v>
+      </c>
+      <c r="C527" t="n">
+        <v>456.32</v>
+      </c>
+      <c r="D527" t="n">
+        <v>448.87</v>
+      </c>
+      <c r="E527" t="n">
+        <v>446.39</v>
+      </c>
+      <c r="F527" t="n">
+        <v>439.49</v>
+      </c>
+      <c r="G527" t="n">
+        <v>435.58</v>
+      </c>
+      <c r="H527" t="n">
+        <v>425.45</v>
+      </c>
+      <c r="I527" t="n">
+        <v>410.9</v>
+      </c>
+      <c r="J527" t="n">
+        <v>407.77</v>
+      </c>
+      <c r="K527" t="n">
+        <v>404.38</v>
+      </c>
+      <c r="L527" t="n">
+        <v>416.9</v>
+      </c>
+      <c r="M527" t="n">
+        <v>422.48</v>
+      </c>
+      <c r="N527" t="n">
+        <v>422.29</v>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>461.98</v>
+      </c>
+      <c r="C528" t="n">
+        <v>457.14</v>
+      </c>
+      <c r="D528" t="n">
+        <v>450.46</v>
+      </c>
+      <c r="E528" t="n">
+        <v>447.66</v>
+      </c>
+      <c r="F528" t="n">
+        <v>441.23</v>
+      </c>
+      <c r="G528" t="n">
+        <v>437.61</v>
+      </c>
+      <c r="H528" t="n">
+        <v>428.02</v>
+      </c>
+      <c r="I528" t="n">
+        <v>410.9</v>
+      </c>
+      <c r="J528" t="n">
+        <v>407.77</v>
+      </c>
+      <c r="K528" t="n">
+        <v>404.38</v>
+      </c>
+      <c r="L528" t="n">
+        <v>416.9</v>
+      </c>
+      <c r="M528" t="n">
+        <v>422.48</v>
+      </c>
+      <c r="N528" t="n">
+        <v>422.29</v>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27062,7 +27368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B548"/>
+  <dimension ref="A1:B554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32545,6 +32851,66 @@
       </c>
       <c r="B548" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -32713,28 +33079,28 @@
         <v>0.031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.177775018828601</v>
+        <v>2.232243665307376</v>
       </c>
       <c r="J2" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6662793095192718</v>
+        <v>0.6723203207811176</v>
       </c>
       <c r="M2" t="n">
-        <v>9.059047607170603</v>
+        <v>9.24397069395059</v>
       </c>
       <c r="N2" t="n">
-        <v>134.7935566022414</v>
+        <v>139.7970072621221</v>
       </c>
       <c r="O2" t="n">
-        <v>11.61006273033188</v>
+        <v>11.82357844572116</v>
       </c>
       <c r="P2" t="n">
-        <v>377.2286105116413</v>
+        <v>376.6662120965244</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32791,28 +33157,28 @@
         <v>0.0365</v>
       </c>
       <c r="I3" t="n">
-        <v>2.223086796736546</v>
+        <v>2.280396307176385</v>
       </c>
       <c r="J3" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6874796701316161</v>
+        <v>0.6919042629539267</v>
       </c>
       <c r="M3" t="n">
-        <v>8.89286293462532</v>
+        <v>9.105309766338667</v>
       </c>
       <c r="N3" t="n">
-        <v>127.7932700588241</v>
+        <v>133.6183269935499</v>
       </c>
       <c r="O3" t="n">
-        <v>11.30456854810585</v>
+        <v>11.55933938395918</v>
       </c>
       <c r="P3" t="n">
-        <v>369.2041079076121</v>
+        <v>368.6137533823451</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32869,28 +33235,28 @@
         <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>2.086298640533878</v>
+        <v>2.138563856499648</v>
       </c>
       <c r="J4" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K4" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.664306095462868</v>
+        <v>0.6703632248652109</v>
       </c>
       <c r="M4" t="n">
-        <v>9.177373655028408</v>
+        <v>9.354838612460563</v>
       </c>
       <c r="N4" t="n">
-        <v>125.1137089265214</v>
+        <v>129.7703898208863</v>
       </c>
       <c r="O4" t="n">
-        <v>11.18542394934235</v>
+        <v>11.39168072853547</v>
       </c>
       <c r="P4" t="n">
-        <v>367.5923407629406</v>
+        <v>367.0539294661594</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32947,28 +33313,28 @@
         <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>2.106896130845866</v>
+        <v>2.16213331354567</v>
       </c>
       <c r="J5" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K5" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6492262608602621</v>
+        <v>0.6555936282774948</v>
       </c>
       <c r="M5" t="n">
-        <v>9.439693601991834</v>
+        <v>9.62926313790495</v>
       </c>
       <c r="N5" t="n">
-        <v>136.4250040674177</v>
+        <v>141.7121473699609</v>
       </c>
       <c r="O5" t="n">
-        <v>11.68011147495681</v>
+        <v>11.904291132611</v>
       </c>
       <c r="P5" t="n">
-        <v>362.0569278019885</v>
+        <v>361.4878756236217</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33025,28 +33391,28 @@
         <v>0.0406</v>
       </c>
       <c r="I6" t="n">
-        <v>2.30719783586745</v>
+        <v>2.361137781182133</v>
       </c>
       <c r="J6" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K6" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6519002095172906</v>
+        <v>0.6592540149397061</v>
       </c>
       <c r="M6" t="n">
-        <v>9.84791664312505</v>
+        <v>10.0347343719888</v>
       </c>
       <c r="N6" t="n">
-        <v>162.0772084257839</v>
+        <v>166.6798501732113</v>
       </c>
       <c r="O6" t="n">
-        <v>12.73095473347478</v>
+        <v>12.91045507227423</v>
       </c>
       <c r="P6" t="n">
-        <v>353.470995926392</v>
+        <v>352.9167054834854</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33103,28 +33469,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>2.322676754314356</v>
+        <v>2.373858780846941</v>
       </c>
       <c r="J7" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K7" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L7" t="n">
-        <v>0.635292535235882</v>
+        <v>0.6437080143775724</v>
       </c>
       <c r="M7" t="n">
-        <v>10.18449895481355</v>
+        <v>10.32189706690228</v>
       </c>
       <c r="N7" t="n">
-        <v>177.4915286116896</v>
+        <v>181.3167009854253</v>
       </c>
       <c r="O7" t="n">
-        <v>13.32259466514273</v>
+        <v>13.46538900238034</v>
       </c>
       <c r="P7" t="n">
-        <v>349.8300751005897</v>
+        <v>349.3049616942948</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33181,28 +33547,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>2.347987514808462</v>
+        <v>2.386437884397574</v>
       </c>
       <c r="J8" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K8" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.64226303007901</v>
+        <v>0.6512480412050412</v>
       </c>
       <c r="M8" t="n">
-        <v>10.18590949265919</v>
+        <v>10.24503790928235</v>
       </c>
       <c r="N8" t="n">
-        <v>175.388330237238</v>
+        <v>176.7032403504528</v>
       </c>
       <c r="O8" t="n">
-        <v>13.24342592523695</v>
+        <v>13.29297710636909</v>
       </c>
       <c r="P8" t="n">
-        <v>344.4055955022934</v>
+        <v>344.010646731506</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33259,28 +33625,28 @@
         <v>0.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>2.190259643533627</v>
+        <v>2.201806767456336</v>
       </c>
       <c r="J9" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K9" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5934374177520625</v>
+        <v>0.6016937108490399</v>
       </c>
       <c r="M9" t="n">
-        <v>10.691933397213</v>
+        <v>10.61719323815436</v>
       </c>
       <c r="N9" t="n">
-        <v>187.7162669290742</v>
+        <v>185.9405515182179</v>
       </c>
       <c r="O9" t="n">
-        <v>13.70095861350855</v>
+        <v>13.63600203572212</v>
       </c>
       <c r="P9" t="n">
-        <v>344.3425100470783</v>
+        <v>344.2238417576104</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33337,28 +33703,28 @@
         <v>0.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1695827359836</v>
+        <v>2.175429874956017</v>
       </c>
       <c r="J10" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K10" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5753072170571576</v>
+        <v>0.5827515493639726</v>
       </c>
       <c r="M10" t="n">
-        <v>10.89282156003614</v>
+        <v>10.79483959136309</v>
       </c>
       <c r="N10" t="n">
-        <v>198.4658178405093</v>
+        <v>196.3249480062443</v>
       </c>
       <c r="O10" t="n">
-        <v>14.087789671929</v>
+        <v>14.01160047982543</v>
       </c>
       <c r="P10" t="n">
-        <v>344.7871901448496</v>
+        <v>344.7270763238007</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33415,28 +33781,28 @@
         <v>0.0305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.152921020087732</v>
+        <v>2.154652768579756</v>
       </c>
       <c r="J11" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K11" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5750460836033673</v>
+        <v>0.5816777066477055</v>
       </c>
       <c r="M11" t="n">
-        <v>10.81430643556329</v>
+        <v>10.71192103962273</v>
       </c>
       <c r="N11" t="n">
-        <v>195.310241675014</v>
+        <v>193.1281810932357</v>
       </c>
       <c r="O11" t="n">
-        <v>13.97534406284919</v>
+        <v>13.89705656220898</v>
       </c>
       <c r="P11" t="n">
-        <v>344.4732227241356</v>
+        <v>344.4553756827309</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33493,28 +33859,28 @@
         <v>0.0259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.108378930051924</v>
+        <v>2.132471700810321</v>
       </c>
       <c r="J12" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K12" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5869568049892531</v>
+        <v>0.5968925151424915</v>
       </c>
       <c r="M12" t="n">
-        <v>10.59628124558223</v>
+        <v>10.5908619574654</v>
       </c>
       <c r="N12" t="n">
-        <v>178.367735885699</v>
+        <v>177.6453150833953</v>
       </c>
       <c r="O12" t="n">
-        <v>13.35543843854252</v>
+        <v>13.3283650566525</v>
       </c>
       <c r="P12" t="n">
-        <v>348.3530271550777</v>
+        <v>348.1054102426301</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33571,28 +33937,28 @@
         <v>0.0364</v>
       </c>
       <c r="I13" t="n">
-        <v>2.052195031102307</v>
+        <v>2.099872443780363</v>
       </c>
       <c r="J13" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K13" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="L13" t="n">
-        <v>0.50426545374945</v>
+        <v>0.5168543874440572</v>
       </c>
       <c r="M13" t="n">
-        <v>11.54776085474913</v>
+        <v>11.67384053746182</v>
       </c>
       <c r="N13" t="n">
-        <v>236.0787336485592</v>
+        <v>238.4284843723082</v>
       </c>
       <c r="O13" t="n">
-        <v>15.36485384403507</v>
+        <v>15.44112963394545</v>
       </c>
       <c r="P13" t="n">
-        <v>345.4403514322374</v>
+        <v>344.9504027580656</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33653,28 +34019,28 @@
         <v>0.0281</v>
       </c>
       <c r="I14" t="n">
-        <v>1.700168307559208</v>
+        <v>1.770570945553339</v>
       </c>
       <c r="J14" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K14" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3771285686566356</v>
+        <v>0.3929517438768442</v>
       </c>
       <c r="M14" t="n">
-        <v>12.90636778905217</v>
+        <v>12.99621055587328</v>
       </c>
       <c r="N14" t="n">
-        <v>273.1823705948286</v>
+        <v>281.0905147553332</v>
       </c>
       <c r="O14" t="n">
-        <v>16.52822950575253</v>
+        <v>16.76575422566289</v>
       </c>
       <c r="P14" t="n">
-        <v>344.9051768848904</v>
+        <v>344.1818843087246</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -33716,7 +34082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O522"/>
+  <dimension ref="A1:O528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73857,6 +74223,468 @@
         </is>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-36.9001176312799,174.4456268051843</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-36.89943906787285,174.44531692202094</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-36.8987592724287,174.44501016317994</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-36.89809003820065,174.4446764840931</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-36.89744442459944,174.4442826148483</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-36.8967762877488,174.4439461117384</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-36.89608329308418,174.44367292174726</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-36.89536009835283,174.44347665366135</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-36.894703959408446,174.4431071151904</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>-36.89404349240967,174.44274828325877</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>-36.893445357267424,174.44223082295116</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>-36.892831502945384,174.44178039858414</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>-36.892207411284076,174.44136616676545</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-36.900113000992235,174.445638601451</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-36.89944247131789,174.44530825132728</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-36.89876065754634,174.4450066344369</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-36.898095064176005,174.44466367989264</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-36.8974416939665,174.44428957141244</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-36.89677197415961,174.4439571010108</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-36.896080879065074,174.44367907165704</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-36.895365282548525,174.44346344659508</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-36.89470655933877,174.44310045405123</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-36.8940468988783,174.44273949025578</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-36.89344703846904,174.44222647554415</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>-36.89283117957411,174.44178120091658</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>-36.892204531251544,174.44137302883604</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-36.900113990370045,174.44563608088131</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-36.89944393559057,174.44530452091232</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-36.89876655418889,174.44499161207224</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-36.89810274164757,174.44464412071702</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-36.897442089710424,174.44428856321477</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-36.896775575413045,174.44394792648072</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-36.89608380754724,174.44367161111072</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-36.89537355351424,174.4434423757757</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-36.89471365005604,174.4430822873057</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-36.894053750968446,174.4427218031784</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-36.89345235575686,174.44221272560446</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>-36.89283526213627,174.4417710714691</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>-36.89220770346126,174.44136547061333</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-36.90011517762334,174.44563305619764</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-36.89944801180852,174.4452941362429</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-36.89877098656328,174.44498032009187</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-36.89811030039226,174.44462486399897</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-36.8974401901395,174.44429340256352</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-36.896775298393564,174.44394863221382</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-36.896086894325265,174.443663747291</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-36.89537925216793,174.44342785807925</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-36.894718810520786,174.44306906594989</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-36.894060955449014,174.44270320647638</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-36.893459471536666,174.44219432494677</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>-36.892839385119004,174.44176084172898</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>-36.892209581743124,174.4413609953496</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-36.900123053068256,174.44561299245993</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-36.89945655999083,174.44527235868003</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-36.89877874321593,174.44496055912302</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-36.898120589778046,174.44459865065923</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-36.897444939066474,174.44428130419124</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-36.89678111580157,174.44393381181737</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-36.89609267213914,174.4436490278318</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-36.895386731648244,174.4434088035993</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-36.89472511337654,174.44305291772656</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-36.894060955449014,174.44270320647638</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-36.893459471536666,174.44219432494677</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>-36.892839385119004,174.44176084172898</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>-36.892209581743124,174.4413609953496</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-36.900127287602615,174.44560220441832</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-36.89945980513309,174.44526409127062</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-36.898785035600156,174.44494452853814</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-36.8981256157452,174.44458584644835</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-36.89745182500843,174.44426376154868</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-36.89678914936206,174.44391334555178</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-36.896102842670196,174.4436231175454</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-36.895386731648244,174.4434088035993</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-36.89472511337654,174.44305291772656</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-36.894060955449014,174.44270320647638</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-36.893459471536666,174.44219432494677</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-36.892839385119004,174.44176084172898</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>-36.892209581743124,174.4413609953496</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
